--- a/docs/audit-2026-10/bilan-1/captures/bilan-temoin.xlsx
+++ b/docs/audit-2026-10/bilan-1/captures/bilan-temoin.xlsx
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="B52" s="11">
-        <f>SUM(F34:F43)</f>
+        <f>SUM(F34:F43)+F25-F43</f>
         <v/>
       </c>
       <c r="C52" s="12" t="n">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="B53" s="11">
-        <f>SUM(D34:D43)</f>
+        <f>SUM(D34:D43)+D25-D43</f>
         <v/>
       </c>
       <c r="C53" s="12" t="n">
